--- a/data/externalStats/RebateRefreshOutput/Consolidated_External_Report_27JulPROD.xlsx
+++ b/data/externalStats/RebateRefreshOutput/Consolidated_External_Report_27JulPROD.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TC4" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,12 +27,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+        <bgColor rgb="00FFCCCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +53,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,6 +429,7192 @@
         <is>
           <t>Table</t>
         </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>excl - total</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>excl - brand</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>excl - generic</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AS66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>excl - total</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Excl - Total</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Excl - Total</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OTCs</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1354</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1408</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2778</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1368.212392840544</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1446.919546415252</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16.81060051458184</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2831.942539770378</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1383.143317400116</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1471.956966580286</v>
+      </c>
+      <c r="N4" t="n">
+        <v>17.34055365383277</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2872.440837634235</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1400.449389437115</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1494.267545410098</v>
+      </c>
+      <c r="S4" t="n">
+        <v>17.72189602814375</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2912.438830875357</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>OTCs</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>1354</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1408</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2778</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1368.212392840543</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1446.919546415253</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>16.81060051458184</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2831.942539770378</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1383.143317400116</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1471.956966580285</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>17.34055365383277</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2872.440837634234</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1400.449389437117</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1494.2675454101</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>17.72189602814375</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2912.438830875361</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vaccines</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9389</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9396</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9604.744793221947</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7.468734608523381</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9612.21352783047</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9711.100612668353</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7.681420291833212</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9718.782032960187</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>9788.465905473882</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7.841870691875744</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9796.307776165759</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Vaccines</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>9389</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>9396</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9604.744793221946</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>7.468734608523375</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>9612.213527830469</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>9711.100612668353</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>7.681420291833214</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>9718.782032960187</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>9788.465905473895</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>7.841870691875751</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9796.307776165771</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Repackaged</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Repackaged</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MSBs</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5352</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1832</v>
+      </c>
+      <c r="D8" t="n">
+        <v>34</v>
+      </c>
+      <c r="E8" t="n">
+        <v>87</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7305</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8942.039540173875</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3500.537314860515</v>
+      </c>
+      <c r="I8" t="n">
+        <v>78.88548020358267</v>
+      </c>
+      <c r="J8" t="n">
+        <v>61.0213332002613</v>
+      </c>
+      <c r="K8" t="n">
+        <v>12582.48366843823</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9792.362202164186</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3892.812180303247</v>
+      </c>
+      <c r="N8" t="n">
+        <v>89.46001460888921</v>
+      </c>
+      <c r="O8" t="n">
+        <v>62.2499783240786</v>
+      </c>
+      <c r="P8" t="n">
+        <v>13836.8843754004</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>11405.71069303371</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4368.403547057688</v>
+      </c>
+      <c r="S8" t="n">
+        <v>106.4689901288691</v>
+      </c>
+      <c r="T8" t="n">
+        <v>63.95802567873019</v>
+      </c>
+      <c r="U8" t="n">
+        <v>15944.541255899</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>MSBs</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>5352</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1832</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>87</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>7305</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>8942.039540173875</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3500.537314860515</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>78.88548020358267</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>61.02133320026134</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>12582.48366843823</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>9792.362202164188</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>3892.812180303247</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>89.46001460888921</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>62.24997832407859</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>13836.8843754004</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>11405.71069303371</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4368.403547057688</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>106.4689901288691</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>63.9580256787302</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>15944.541255899</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Non FDA Approved</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Non FDA Approved</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LDD</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1211</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1431.027434888835</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1431.027434888835</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1572.645185877546</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1572.645185877546</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1698.361346924144</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1698.361346924144</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>LDD</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1211</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1211</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1431.027434888835</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1431.027434888835</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1572.645185877547</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1572.645185877547</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1698.361346924144</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1698.361346924144</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Institutional NDCs</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Institutional NDCs</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Formulary Exclusions</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4585</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3184</v>
+      </c>
+      <c r="D12" t="n">
+        <v>32</v>
+      </c>
+      <c r="E12" t="n">
+        <v>91</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7892</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5685.339040584902</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4472.570348548972</v>
+      </c>
+      <c r="I12" t="n">
+        <v>51.71639126361768</v>
+      </c>
+      <c r="J12" t="n">
+        <v>109.2666359584575</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10318.89241635595</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6423.034571778222</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5335.215808095964</v>
+      </c>
+      <c r="N12" t="n">
+        <v>65.60802877947428</v>
+      </c>
+      <c r="O12" t="n">
+        <v>118.6178170830754</v>
+      </c>
+      <c r="P12" t="n">
+        <v>11942.47622573673</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6613.078984960881</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5523.444075919046</v>
+      </c>
+      <c r="S12" t="n">
+        <v>68.39432747769432</v>
+      </c>
+      <c r="T12" t="n">
+        <v>130.2899097988911</v>
+      </c>
+      <c r="U12" t="n">
+        <v>12335.20729815651</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Formulary Exclusions</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>4585</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3184</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>91</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>7892</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>5685.339040584902</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>4472.570348548973</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>51.71639126361766</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>109.2666359584576</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>10318.89241635595</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>6423.034571778222</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>5335.215808095963</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>65.60802877947431</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>118.6178170830753</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>11942.47622573673</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>6613.078984960885</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>5523.444075919049</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>68.39432747769432</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>130.2899097988911</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>12335.20729815652</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Synthroid</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Synthroid</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1695</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1331</v>
+      </c>
+      <c r="D14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3051</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2399.052334449079</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1992.31258498822</v>
+      </c>
+      <c r="I14" t="n">
+        <v>33.57613890171297</v>
+      </c>
+      <c r="J14" t="n">
+        <v>210.3076008311627</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4635.248659170175</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2826.131680913328</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2417.817724958295</v>
+      </c>
+      <c r="N14" t="n">
+        <v>40.46397792001835</v>
+      </c>
+      <c r="O14" t="n">
+        <v>232.0624315905739</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5516.475815382215</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3333.582500652527</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2919.677575700363</v>
+      </c>
+      <c r="S14" t="n">
+        <v>48.29562868547146</v>
+      </c>
+      <c r="T14" t="n">
+        <v>251.2530014457652</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6552.808706484127</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>1695</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1331</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3051</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2399.052334449065</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1992.312584988211</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>33.57613890171319</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>210.3076008311631</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>4635.248659170152</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2826.131680913324</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2417.817724958292</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>40.463977920018</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>232.0624315905736</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>5516.475815382208</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>3333.582500652556</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2919.67757570038</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>48.29562868547177</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>251.2530014457654</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6552.808706484172</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.251182157495163</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.251182157495163</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.349719893363836</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.349719893363836</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.471866739605949</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.471866739605949</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.251182157495164</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.251182157495164</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2.349719893363836</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.349719893363836</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.47186673960595</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.47186673960595</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MFP 2026, 2027</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="1" t="inlineStr">
+        <is>
+          <t>MFP 2026 &amp; 2027</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="1" t="inlineStr">
+        <is>
+          <t>ENTER DESC</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Non-Rebatable</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>213999.7374377511</v>
+      </c>
+      <c r="H18" t="n">
+        <v>224568.4320475684</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3516.692006174286</v>
+      </c>
+      <c r="J18" t="n">
+        <v>522.2085919510268</v>
+      </c>
+      <c r="K18" t="n">
+        <v>442607.0700834447</v>
+      </c>
+      <c r="L18" t="n">
+        <v>217243.1407753343</v>
+      </c>
+      <c r="M18" t="n">
+        <v>229187.5867689243</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3573.782708252549</v>
+      </c>
+      <c r="O18" t="n">
+        <v>536.567103549567</v>
+      </c>
+      <c r="P18" t="n">
+        <v>450541.0773560607</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>219196.1918988632</v>
+      </c>
+      <c r="R18" t="n">
+        <v>232233.6148168273</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3604.587454448593</v>
+      </c>
+      <c r="T18" t="n">
+        <v>603.1636250341775</v>
+      </c>
+      <c r="U18" t="n">
+        <v>455637.5577951731</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Non-Rebatable</t>
+        </is>
+      </c>
+      <c r="Z18" s="1" t="inlineStr"/>
+      <c r="AA18" s="1" t="inlineStr"/>
+      <c r="AB18" s="1" t="inlineStr"/>
+      <c r="AC18" s="1" t="inlineStr"/>
+      <c r="AD18" s="1" t="inlineStr"/>
+      <c r="AE18" t="n">
+        <v>213999.7374377511</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>224568.4320475684</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3516.692006174286</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>522.208591951027</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>442607.0700834447</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>217243.1407753343</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>229187.5867689242</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>3573.782708252549</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>536.5671035495672</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>450541.0773560606</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>219196.1918988632</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>232233.6148168273</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>3604.587454448593</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>603.1636250341774</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>455637.5577951732</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>22375</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7762</v>
+      </c>
+      <c r="D19" t="n">
+        <v>105</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1391</v>
+      </c>
+      <c r="F19" t="n">
+        <v>31635</v>
+      </c>
+      <c r="G19" t="n">
+        <v>241999.1255390214</v>
+      </c>
+      <c r="H19" t="n">
+        <v>235988.2405769899</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3697.680617057782</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2333.831596829744</v>
+      </c>
+      <c r="K19" t="n">
+        <v>484021.1295120562</v>
+      </c>
+      <c r="L19" t="n">
+        <v>247378.9131602585</v>
+      </c>
+      <c r="M19" t="n">
+        <v>242313.0708691539</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3786.655283214763</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2522.142516424841</v>
+      </c>
+      <c r="P19" t="n">
+        <v>496003.1315489453</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>251737.4793724213</v>
+      </c>
+      <c r="R19" t="n">
+        <v>246547.2494316063</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3845.468296768772</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2747.025908881708</v>
+      </c>
+      <c r="U19" t="n">
+        <v>504879.6948764176</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>22375</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>7762</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1391</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>31635</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>241999.1255390214</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>235988.2405769899</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3697.680617057782</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2333.831596829744</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>484021.1295120562</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>247378.9131602585</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>242313.0708691539</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>3786.655283214763</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2522.142516424841</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>496003.1315489453</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>251737.4793724214</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>246547.2494316064</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3845.468296768772</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2747.025908881708</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>504879.6948764178</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Removed Claims</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>3772</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Removed Claims</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="n">
+        <v>3772</v>
+      </c>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>523801</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="n">
+        <v>523801</v>
+      </c>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>excl - brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Base Yr</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Base Yr</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>2027</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="n">
+        <v>2028</v>
+      </c>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="n">
+        <v>2029</v>
+      </c>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Excl - Brand</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Excl - Brand</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OTCs</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1403</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2766</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1360.461874663778</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1442.583703144495</v>
+      </c>
+      <c r="I29" t="n">
+        <v>16.81060051458184</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2819.856178322855</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1374.950469289653</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1467.885546217304</v>
+      </c>
+      <c r="N29" t="n">
+        <v>17.34055365383277</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2860.176569160789</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1391.76658933676</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1490.435200163811</v>
+      </c>
+      <c r="S29" t="n">
+        <v>17.72189602814375</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2899.923685528714</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>OTCs</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>1347</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1403</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2766</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1360.461874663778</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1442.583703144495</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>16.81060051458184</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2819.856178322855</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1374.950469289653</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1467.885546217303</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>17.34055365383277</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2860.176569160788</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1391.766589336762</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1490.435200163812</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>17.72189602814375</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2899.923685528719</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Vaccines</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>9389</v>
+      </c>
+      <c r="C31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9396</v>
+      </c>
+      <c r="G31" t="n">
+        <v>9604.744793221947</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7.468734608523381</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>9612.21352783047</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9711.100612668353</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7.681420291833212</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>9718.782032960187</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>9788.465905473882</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7.841870691875744</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>9796.307776165759</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Vaccines</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>9389</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>9396</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9604.744793221946</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>7.468734608523375</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>9612.213527830469</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>9711.100612668353</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>7.681420291833214</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>9718.782032960187</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>9788.465905473895</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>7.841870691875751</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>9796.307776165771</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Repackaged</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Repackaged</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MSBs</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2931</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1459</v>
+      </c>
+      <c r="D33" t="n">
+        <v>29</v>
+      </c>
+      <c r="E33" t="n">
+        <v>87</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4506</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1744.054218418618</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1050.980920266797</v>
+      </c>
+      <c r="I33" t="n">
+        <v>13.46605752084745</v>
+      </c>
+      <c r="J33" t="n">
+        <v>41.96486816008202</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2850.466064366344</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1635.212972539078</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1001.385901888838</v>
+      </c>
+      <c r="N33" t="n">
+        <v>11.50133525344111</v>
+      </c>
+      <c r="O33" t="n">
+        <v>41.68803870239996</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2689.788248383757</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1409.614172356642</v>
+      </c>
+      <c r="R33" t="n">
+        <v>964.220387968111</v>
+      </c>
+      <c r="S33" t="n">
+        <v>9.804214882119291</v>
+      </c>
+      <c r="T33" t="n">
+        <v>42.13077516565711</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2425.76955037253</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>MSBs</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>2931</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1459</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>87</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>4506</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1744.054218418618</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1050.980920266795</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>13.46605752084745</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>41.96486816008206</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2850.466064366343</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1635.212972539078</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1001.385901888838</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>11.50133525344111</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>41.68803870239995</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2689.788248383757</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1409.614172356645</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>964.2203879681115</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>9.804214882119291</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>42.13077516565713</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2425.769550372533</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Non FDA Approved</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Non FDA Approved</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LDD</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1143</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1251.272016547032</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1251.272016547032</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1340.040023429968</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1340.040023429968</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1395.880080084951</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1395.880080084951</v>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>LDD</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1143</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1143</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1251.272016547032</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1251.272016547032</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1340.040023429968</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1340.040023429968</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1395.880080084951</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1395.880080084951</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Institutional NDCs</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Institutional NDCs</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Formulary Exclusions</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2579</v>
+      </c>
+      <c r="C37" t="n">
+        <v>785</v>
+      </c>
+      <c r="D37" t="n">
+        <v>22</v>
+      </c>
+      <c r="E37" t="n">
+        <v>68</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3454</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3475.770490677582</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1879.236665364517</v>
+      </c>
+      <c r="I37" t="n">
+        <v>40.88056000062586</v>
+      </c>
+      <c r="J37" t="n">
+        <v>83.07733275588407</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5478.965048798609</v>
+      </c>
+      <c r="L37" t="n">
+        <v>4130.131957310844</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2671.817886250132</v>
+      </c>
+      <c r="N37" t="n">
+        <v>54.47014864180034</v>
+      </c>
+      <c r="O37" t="n">
+        <v>91.05240222120837</v>
+      </c>
+      <c r="P37" t="n">
+        <v>6947.472394423986</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4273.151023763346</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2806.341432842153</v>
+      </c>
+      <c r="S37" t="n">
+        <v>57.02415701411742</v>
+      </c>
+      <c r="T37" t="n">
+        <v>101.0761670850872</v>
+      </c>
+      <c r="U37" t="n">
+        <v>7237.592780704703</v>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Formulary Exclusions</t>
+        </is>
+      </c>
+      <c r="Z37" t="n">
+        <v>2579</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>785</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>68</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3454</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>3475.770490677582</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1879.236665364516</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>40.88056000062584</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>83.07733275588413</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>5478.965048798608</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>4130.131957310843</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>2671.817886250132</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>54.47014864180036</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>91.05240222120834</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>6947.472394423984</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>4273.151023763349</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>2806.341432842156</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>57.02415701411741</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>101.0761670850872</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>7237.592780704709</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Synthroid</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Synthroid</t>
+        </is>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1695</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1331</v>
+      </c>
+      <c r="D39" t="n">
+        <v>23</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3051</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2399.052334449065</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1992.312584988213</v>
+      </c>
+      <c r="I39" t="n">
+        <v>33.57613890171315</v>
+      </c>
+      <c r="J39" t="n">
+        <v>209.6733577939747</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4634.614416132966</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2826.131680913324</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2417.817724958292</v>
+      </c>
+      <c r="N39" t="n">
+        <v>40.46397792001801</v>
+      </c>
+      <c r="O39" t="n">
+        <v>231.3531612844695</v>
+      </c>
+      <c r="P39" t="n">
+        <v>5515.766545076103</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3333.582500652556</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2919.677575700378</v>
+      </c>
+      <c r="S39" t="n">
+        <v>48.29562868547174</v>
+      </c>
+      <c r="T39" t="n">
+        <v>250.4907355877558</v>
+      </c>
+      <c r="U39" t="n">
+        <v>6552.046440626161</v>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="Z39" t="n">
+        <v>1695</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1331</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>3051</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2399.052334449065</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1992.312584988211</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>33.57613890171319</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>209.6733577939749</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>4634.614416132964</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>2826.131680913324</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2417.817724958292</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>40.463977920018</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>231.3531612844695</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>5515.766545076103</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>3333.582500652556</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>2919.67757570038</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>48.29562868547177</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>250.490735587756</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>6552.046440626163</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.616939120306969</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.616939120306969</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.640449587259669</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.640449587259669</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.709600881596582</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.709600881596582</v>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.61693912030697</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.61693912030697</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.640449587259669</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.640449587259669</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.709600881596582</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.709600881596582</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>MFP 2026, 2027</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="1" t="inlineStr">
+        <is>
+          <t>MFP 2026 &amp; 2027</t>
+        </is>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ENTER DESC</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>ENTER DESC</t>
+        </is>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Non-Rebatable</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1900.278059066835</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1114.495647238113</v>
+      </c>
+      <c r="I43" t="n">
+        <v>22.34085682814803</v>
+      </c>
+      <c r="J43" t="n">
+        <v>193.8046836844156</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3230.919246817512</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1376.520340781329</v>
+      </c>
+      <c r="M43" t="n">
+        <v>474.1870466229238</v>
+      </c>
+      <c r="N43" t="n">
+        <v>10.15020924840391</v>
+      </c>
+      <c r="O43" t="n">
+        <v>195.924632515909</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2056.782229168566</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1409.311208536868</v>
+      </c>
+      <c r="R43" t="n">
+        <v>497.2231949594199</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10.97973574079871</v>
+      </c>
+      <c r="T43" t="n">
+        <v>208.2943256733983</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2125.808464910485</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Non-Rebatable</t>
+        </is>
+      </c>
+      <c r="Z43" s="1" t="inlineStr"/>
+      <c r="AA43" s="1" t="inlineStr"/>
+      <c r="AB43" s="1" t="inlineStr"/>
+      <c r="AC43" s="1" t="inlineStr"/>
+      <c r="AD43" s="1" t="inlineStr"/>
+      <c r="AE43" t="n">
+        <v>1900.278059066834</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1114.495647238112</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>22.34085682814803</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>193.8046836844156</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>3230.91924681751</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1376.52034078133</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>474.1870466229238</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>10.15020924840391</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>195.9246325159089</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>2056.782229168567</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>1409.31120853687</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>497.2231949594202</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>10.97973574079871</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>208.2943256733983</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>2125.808464910487</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>17941</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4985</v>
+      </c>
+      <c r="D44" t="n">
+        <v>90</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F44" t="n">
+        <v>24318</v>
+      </c>
+      <c r="G44" t="n">
+        <v>20484.36177049782</v>
+      </c>
+      <c r="H44" t="n">
+        <v>7487.078255610657</v>
+      </c>
+      <c r="I44" t="n">
+        <v>127.0742137659163</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1779.792258941388</v>
+      </c>
+      <c r="K44" t="n">
+        <v>29879.92343793609</v>
+      </c>
+      <c r="L44" t="n">
+        <v>21054.04803350258</v>
+      </c>
+      <c r="M44" t="n">
+        <v>8040.775526229323</v>
+      </c>
+      <c r="N44" t="n">
+        <v>133.9262247174962</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1900.058258153955</v>
+      </c>
+      <c r="P44" t="n">
+        <v>31130.44849219062</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>21605.89140012005</v>
+      </c>
+      <c r="R44" t="n">
+        <v>8685.739662325748</v>
+      </c>
+      <c r="S44" t="n">
+        <v>143.8256323506509</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1997.87208359685</v>
+      </c>
+      <c r="U44" t="n">
+        <v>32435.0383792749</v>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Z44" t="n">
+        <v>17941</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4985</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1300</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>24318</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>20484.36177049782</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>7487.078255610653</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>127.0742137659164</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1779.792258941389</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>29879.92343793609</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>21054.04803350258</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>8040.775526229323</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>133.9262247174962</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1900.058258153955</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>31130.44849219062</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>21605.89140012008</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>8685.739662325755</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>143.8256323506509</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1997.87208359685</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>32435.03837927493</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>excl - generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Excl - Generic</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Excl - Generic</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>R90</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>OTCs</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>12</v>
+      </c>
+      <c r="G51" t="n">
+        <v>7.750518176765181</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4.335843270757448</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>12.08636144752263</v>
+      </c>
+      <c r="L51" t="n">
+        <v>8.192848110463444</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.071420362981854</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>12.2642684734453</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>8.682800100355177</v>
+      </c>
+      <c r="R51" t="n">
+        <v>3.832345246287813</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>12.51514534664299</v>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>OTCs</t>
+        </is>
+      </c>
+      <c r="Z51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>7.750518176765181</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>4.33584327075745</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>12.08636144752263</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>8.192848110463446</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>4.071420362981853</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>12.2642684734453</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>8.682800100355173</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>3.832345246287814</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>12.51514534664299</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Vaccines</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Vaccines</t>
+        </is>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Repackaged</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Repackaged</t>
+        </is>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MSBs</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2421</v>
+      </c>
+      <c r="C55" t="n">
+        <v>373</v>
+      </c>
+      <c r="D55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2799</v>
+      </c>
+      <c r="G55" t="n">
+        <v>7197.985321755256</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2449.556394593719</v>
+      </c>
+      <c r="I55" t="n">
+        <v>65.41942268273522</v>
+      </c>
+      <c r="J55" t="n">
+        <v>19.05646504017928</v>
+      </c>
+      <c r="K55" t="n">
+        <v>9732.017604071889</v>
+      </c>
+      <c r="L55" t="n">
+        <v>8157.149229625108</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2891.42627841441</v>
+      </c>
+      <c r="N55" t="n">
+        <v>77.9586793554481</v>
+      </c>
+      <c r="O55" t="n">
+        <v>20.56193962167864</v>
+      </c>
+      <c r="P55" t="n">
+        <v>11147.09612701664</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>9996.096520677071</v>
+      </c>
+      <c r="R55" t="n">
+        <v>3404.183159089577</v>
+      </c>
+      <c r="S55" t="n">
+        <v>96.66477524674977</v>
+      </c>
+      <c r="T55" t="n">
+        <v>21.82725051307308</v>
+      </c>
+      <c r="U55" t="n">
+        <v>13518.77170552647</v>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>MSBs</t>
+        </is>
+      </c>
+      <c r="Z55" t="n">
+        <v>2421</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>373</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>2799</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>7197.985321755257</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2449.55639459372</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>65.41942268273522</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>19.05646504017929</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>9732.017604071891</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>8157.14922962511</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>2891.426278414408</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>77.9586793554481</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>20.56193962167864</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>11147.09612701664</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>9996.096520677069</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>3404.183159089577</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>96.66477524674978</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>21.82725051307307</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>13518.77170552647</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Non FDA Approved</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Non FDA Approved</t>
+        </is>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>LDD</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>68</v>
+      </c>
+      <c r="F57" t="n">
+        <v>68</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>179.755418341803</v>
+      </c>
+      <c r="K57" t="n">
+        <v>179.755418341803</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>232.6051624475786</v>
+      </c>
+      <c r="P57" t="n">
+        <v>232.6051624475786</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>302.4812668391931</v>
+      </c>
+      <c r="U57" t="n">
+        <v>302.4812668391931</v>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>LDD</t>
+        </is>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>68</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>68</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>179.755418341803</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>179.755418341803</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>232.6051624475786</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>232.6051624475786</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>302.481266839193</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>302.481266839193</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Institutional NDCs</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Institutional NDCs</t>
+        </is>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Formulary Exclusions</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2399</v>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="n">
+        <v>23</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4438</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2209.568549907321</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2593.333683184455</v>
+      </c>
+      <c r="I59" t="n">
+        <v>10.83583126299182</v>
+      </c>
+      <c r="J59" t="n">
+        <v>26.18930320257346</v>
+      </c>
+      <c r="K59" t="n">
+        <v>4839.927367557341</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2292.902614467378</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2663.397921845832</v>
+      </c>
+      <c r="N59" t="n">
+        <v>11.13788013767394</v>
+      </c>
+      <c r="O59" t="n">
+        <v>27.565414861867</v>
+      </c>
+      <c r="P59" t="n">
+        <v>4995.003831312752</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2339.927961197536</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2717.102643076893</v>
+      </c>
+      <c r="S59" t="n">
+        <v>11.3701704635769</v>
+      </c>
+      <c r="T59" t="n">
+        <v>29.21374271380387</v>
+      </c>
+      <c r="U59" t="n">
+        <v>5097.61451745181</v>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Formulary Exclusions</t>
+        </is>
+      </c>
+      <c r="Z59" t="n">
+        <v>2006</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>2399</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>4438</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>2209.56854990732</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>2593.333683184457</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>10.83583126299182</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>26.18930320257346</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>4839.927367557342</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>2292.902614467378</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>2663.397921845831</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>11.13788013767394</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>27.565414861867</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>4995.003831312751</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>2339.927961197535</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>2717.102643076893</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>11.3701704635769</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>29.21374271380386</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>5097.61451745181</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Synthroid</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Synthroid</t>
+        </is>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.6342430371881846</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.6342430371881846</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.7092703061041448</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.7092703061041448</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.7622658580094139</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.7622658580094139</v>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0.6342430371881846</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0.6342430371881846</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>0.7092703061041448</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>0.7092703061041448</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>0.7622658580094139</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>0.7622658580094139</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.6342430371881935</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.6342430371881935</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.7092703061041666</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.7092703061041666</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.7622658580093674</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0.7622658580093674</v>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0.6342430371881935</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0.6342430371881935</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>0.7092703061041666</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>0.7092703061041666</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>0.7622658580093672</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>0.7622658580093672</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>MFP 2026, 2027</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="1" t="inlineStr">
+        <is>
+          <t>MFP 2026 &amp; 2027</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="1" t="inlineStr">
+        <is>
+          <t>ENTER DESC</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Non-Rebatable</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>212099.4593786842</v>
+      </c>
+      <c r="H65" t="n">
+        <v>223453.9364003303</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3494.351149346138</v>
+      </c>
+      <c r="J65" t="n">
+        <v>328.4039082666113</v>
+      </c>
+      <c r="K65" t="n">
+        <v>439376.1508366273</v>
+      </c>
+      <c r="L65" t="n">
+        <v>215866.620434553</v>
+      </c>
+      <c r="M65" t="n">
+        <v>228713.3997223013</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3563.632499004145</v>
+      </c>
+      <c r="O65" t="n">
+        <v>340.6424710336581</v>
+      </c>
+      <c r="P65" t="n">
+        <v>448484.2951268921</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>217786.8806903263</v>
+      </c>
+      <c r="R65" t="n">
+        <v>231736.3916218678</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3593.607718707794</v>
+      </c>
+      <c r="T65" t="n">
+        <v>394.8692993607792</v>
+      </c>
+      <c r="U65" t="n">
+        <v>453511.7493302627</v>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Non-Rebatable</t>
+        </is>
+      </c>
+      <c r="Z65" s="1" t="inlineStr"/>
+      <c r="AA65" s="1" t="inlineStr"/>
+      <c r="AB65" s="1" t="inlineStr"/>
+      <c r="AC65" s="1" t="inlineStr"/>
+      <c r="AD65" s="1" t="inlineStr"/>
+      <c r="AE65" t="n">
+        <v>212099.4593786842</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>223453.9364003303</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>3494.351149346138</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>328.4039082666113</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>439376.1508366273</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>215866.620434553</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>228713.3997223013</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>3563.632499004145</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>340.6424710336582</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>448484.2951268921</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>217786.8806903263</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>231736.3916218678</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>3593.607718707794</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>394.8692993607791</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>453511.7493302628</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4434</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2777</v>
+      </c>
+      <c r="D66" t="n">
+        <v>15</v>
+      </c>
+      <c r="E66" t="n">
+        <v>91</v>
+      </c>
+      <c r="F66" t="n">
+        <v>7317</v>
+      </c>
+      <c r="G66" t="n">
+        <v>221514.7637685236</v>
+      </c>
+      <c r="H66" t="n">
+        <v>228501.1623213792</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3570.606403291865</v>
+      </c>
+      <c r="J66" t="n">
+        <v>554.0393378883552</v>
+      </c>
+      <c r="K66" t="n">
+        <v>454141.2060741202</v>
+      </c>
+      <c r="L66" t="n">
+        <v>226324.8651267559</v>
+      </c>
+      <c r="M66" t="n">
+        <v>234272.2953429246</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3652.729058497267</v>
+      </c>
+      <c r="O66" t="n">
+        <v>622.0842582708865</v>
+      </c>
+      <c r="P66" t="n">
+        <v>464872.6830567548</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>230131.5879723013</v>
+      </c>
+      <c r="R66" t="n">
+        <v>237861.5097692806</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3701.642664418121</v>
+      </c>
+      <c r="T66" t="n">
+        <v>749.1538252848586</v>
+      </c>
+      <c r="U66" t="n">
+        <v>472444.6564971429</v>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>4434</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2777</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>91</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>7317</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>221514.7637685236</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>228501.1623213792</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>3570.606403291865</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>554.0393378883552</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>454141.2060741202</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>226324.8651267559</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>234272.2953429245</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>3652.729058497267</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>622.0842582708867</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>464872.6830567547</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>230131.5879723013</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>237861.5097692806</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>3701.642664418121</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>749.1538252848584</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>472444.6564971429</v>
       </c>
     </row>
   </sheetData>
